--- a/3 четверть_1_Java Core.xlsx
+++ b/3 четверть_1_Java Core.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Machenike\Desktop\Homework_repo\GB_Developer_Workbook\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Machenike\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9101555E-00D9-4D3A-B9D0-9917482C2056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EAA8161-80F2-4642-A319-A0B75F879131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15050" windowHeight="13800" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Название 1-3" sheetId="12" r:id="rId1"/>
+    <sheet name="JavaRush" sheetId="14" r:id="rId2"/>
+    <sheet name="JavaRush (структуры данных)" sheetId="15" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="1071">
   <si>
     <t>Урок 1 часть 1</t>
   </si>
@@ -9859,17 +9861,1814 @@
         int value = in.read();
         System.out.println("First element is - " + value);</t>
   </si>
+  <si>
+    <t>JavaRush</t>
+  </si>
+  <si>
+    <t>`https://javarush.com/groups/posts/equals-java-sravnenie-strok</t>
+  </si>
+  <si>
+    <t>Equals в Java и String compare - Сравнение строк</t>
+  </si>
+  <si>
+    <t>Как и метод toString(), который мы разбирали ранее, equals() принадлежит классу Object</t>
+  </si>
+  <si>
+    <t>equals()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">по умолчанию сравнивает </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ссылки на объекты</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+public boolean equals(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Object ob</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>j) {
+   return (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>this</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> == obj);
+}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>public class Man {
+   int dnaCode;
+   public boolean equals(</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Man man</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) {
+       return </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>this.dnaCode</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ==  man.dnaCode;
+   }
+   public static void main(String[] args) {
+       Man man1 = new Man();
+       man1.dnaCode = 1111222233;
+       Man man2 = new Man();
+       man2.dnaCode = 1111222233;
+       System.out.println(man1.equals(man2));
+   }
+}</t>
+    </r>
+  </si>
+  <si>
+    <t>Переопределяем equals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       String s1 = "JavaRush - лучший сайт для изучения Java!";
+       String s2 = new String("JavaRush - лучший сайт для изучения Java!");
+       System.out.println(s1 == s2);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       String s1 = "JavaRush - лучший сайт для изучения Java!";
+       String s2 = "JavaRush - лучший сайт для изучения Java!";
+       System.out.println(s1 == s2);
+</t>
+  </si>
+  <si>
+    <t>false</t>
+  </si>
+  <si>
+    <t>true</t>
+  </si>
+  <si>
+    <t>true
+если s1 == s2 возвращает true, у этих двух строк одинаковый адрес в памяти.</t>
+  </si>
+  <si>
+    <t>String pool</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>String pool</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Пул строк это область для хранения всех строковых значений, которые ты создаешь в своей программе. С целью экономии памяти и нужен String Pool
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Однако!</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Оператор new при создании объекта принудительно выделяет для него новую область в памяти. </t>
+    </r>
+  </si>
+  <si>
+    <t>equalsIgnoreCase()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">       String address1 = "г. Москва, ул. Академика Королева, дом 12";
+       String address2 = new String("Г. МОСКВА, УЛ. АКАДЕМИКА КОРОЛЕВА, ДОМ 12");
+       System.out.println(address1.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>equalsIgnoreCase</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(address2));</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">       String s1 = "JavaRush - лучший сайт для изучения Java!";
+       String s2 = new String("JavaRush - лучший сайт для изучения Java!");
+       System.out.println(s1.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>equals</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(s2));</t>
+    </r>
+  </si>
+  <si>
+    <t>intern()</t>
+  </si>
+  <si>
+    <t>Метод intern() напрямую работает со String Pool’ом. Если ты вызываешь метод intern() у какой-то строки, он:
+1 Смотрит, есть ли строка с таким текстом в пуле строк.
+2 Если есть, возвращает ссылку на нее в пуле.
+3 Если же нет, помещает строку с этим текстом в пул строк и возвращает ссылку на нее.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Идеальный для сравнения строк, но все же </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>очень опасный</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Риск утечки памяти и нагрузка на GC</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+Если вы начнете интернировать все строки подряд (например, данные от пользователей, строки из базы или динамические ID), пул строк разрастется до огромных размеров. Хотя в современных версиях Java пул находится в Heap и очищается сборщиком мусора (Garbage Collector), гигантский пул строк создает на GC колоссальную нагрузку, что может приводить к микрофризам приложения.</t>
+    </r>
+  </si>
+  <si>
+    <t>Способ сравнения</t>
+  </si>
+  <si>
+    <t>Что сравнивает</t>
+  </si>
+  <si>
+    <t>Результат для строк с одинаковым текстом</t>
+  </si>
+  <si>
+    <t>==</t>
+  </si>
+  <si>
+    <t>ссылки (адреса в памяти)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">true только если это один объект (например два литерала из пула); для </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>new String()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF151F33"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> будет false</t>
+    </r>
+  </si>
+  <si>
+    <t>содержимое (текст)</t>
+  </si>
+  <si>
+    <t>true, если текст совпадает</t>
+  </si>
+  <si>
+    <t>содержимое без учета регистра</t>
+  </si>
+  <si>
+    <t>true, даже если различается регистр</t>
+  </si>
+  <si>
+    <r>
+      <t>==</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF151F33"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> после </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+        <charset val="204"/>
+      </rPr>
+      <t>intern()</t>
+    </r>
+  </si>
+  <si>
+    <t>ссылки после помещения строки в пул</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">       String s1 = "JavaRush - лучший сайт для изучения Java!";
+       String s2 = new String("JavaRush - лучший сайт для изучения Java!");
+       System.out.println(s1 == s2.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intern</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>());</t>
+    </r>
+  </si>
+  <si>
+    <t>Сравнение вещественных чисел</t>
+  </si>
+  <si>
+    <t>`https://javarush.com/groups/posts/2136-ustroystvo-vejshestvennihkh-chisel</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">       if (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Math.abs(f1 - f2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> &lt; threshold)
+           System.out.println("f1 и f2 равны");
+       else
+           System.out.println("f1 и f2 не равны");</t>
+    </r>
+  </si>
+  <si>
+    <t>У нас есть специальное «пороговое» число, 0.0001, одна десятитысячная. Оно может быть и другим. Это зависит от того, насколько точное сравнение тебе нужно в конкретном случае. Можно сделать его и больше, и меньше.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Сравнение по порогу работает так:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+вычитаем одно число из другого;
+берем модуль результата через Math.abs() (значение числа независимо от знака: например, у -5 и 5 модуль одинаковый и равен 5);
+если модуль меньше порога, считаем числа равными.</t>
+    </r>
+  </si>
+  <si>
+    <t>BigDecimal</t>
+  </si>
+  <si>
+    <t>Math.abs(f1 - f2) &lt; threshold</t>
+  </si>
+  <si>
+    <t>Еще один хороший способ сравнения вещественных чисел это специальный класс BigDecimal. Этот класс специально был создан для хранения очень больших чисел с дробной частью.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">В отличие от double и float, при использовании BigDecimal сложение, вычитание и прочие математические операции выполняются </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>не с помощью операторов (+- и т.д.)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>а с помощью методов.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">       BigDecimal f2 = new </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BigDecimal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">(0.1);
+       BigDecimal eleven = new </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>BigDecimal</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(11);
+       f2 = f2.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>multiply</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(eleven);</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">       /*Еще одна особенность BigDecimal - объекты чисел нужно сравнивать между
+       собой с помощью специального метода compareTo()*/
+       if (f1.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>compareTo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(f2) == 0)
+           System.out.println("f1 и f2 равны");
+       else
+           System.out.println("f1 и f2 не равны");</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BigDecimal.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>compareTo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(BigDecimal)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>BigDecimal.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>multiply</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(BigDecimal)</t>
+    </r>
+  </si>
+  <si>
+    <t>Тип</t>
+  </si>
+  <si>
+    <t>Размер</t>
+  </si>
+  <si>
+    <t>Точность</t>
+  </si>
+  <si>
+    <t>Когда использовать</t>
+  </si>
+  <si>
+    <t>float</t>
+  </si>
+  <si>
+    <t>около 7 знаков после запятой</t>
+  </si>
+  <si>
+    <t>когда важна экономия памяти, а высокая точность не критична</t>
+  </si>
+  <si>
+    <t>double</t>
+  </si>
+  <si>
+    <t>около 16 знаков после запятой</t>
+  </si>
+  <si>
+    <t>стандартный выбор для дробных чисел в большинстве задач</t>
+  </si>
+  <si>
+    <t>ограничен только памятью</t>
+  </si>
+  <si>
+    <t>произвольная</t>
+  </si>
+  <si>
+    <t>когда нужна максимальная точность, например в финансовых расчетах</t>
+  </si>
+  <si>
+    <t>64 бита - 8 байт</t>
+  </si>
+  <si>
+    <t>32 бита - 4 байта</t>
+  </si>
+  <si>
+    <t>Принципы ООП</t>
+  </si>
+  <si>
+    <r>
+      <t>Абстракция</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF151F33"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>: выделяем главные характеристики объекта и отбрасываем несущественные.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Наследование</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF151F33"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>: новый класс берет поля и методы существующего (родительского), это повторное использование кода.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Инкапсуляция</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF151F33"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>: прячем внутренние данные класса и даем доступ только через открытые методы.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Полиморфизм</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF151F33"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>: с объектами разных типов работаем через общий интерфейс, а поведение зависит от конкретного типа.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Класс</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF151F33"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> это шаблон (чертеж), а </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF151F33"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t>объект</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF151F33"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="204"/>
+      </rPr>
+      <t xml:space="preserve"> это экземпляр класса, созданный по этому шаблону.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Википедия дает такое </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">определение ООП: </t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Объе́ктно-ориенти́рованное программи́рование (ООП</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>) это методология программирования, основанная на представлении программы в виде совокупности объектов, каждый из которых является экземпляром определенного класса, а классы образуют иерархию наследования.</t>
+    </r>
+  </si>
+  <si>
+    <t>Принцип</t>
+  </si>
+  <si>
+    <t>Суть</t>
+  </si>
+  <si>
+    <t>Пример из статьи</t>
+  </si>
+  <si>
+    <t>выделить главное, отбросить второстепенное</t>
+  </si>
+  <si>
+    <t>у телефона главное это звонить и принимать вызов</t>
+  </si>
+  <si>
+    <t>Наследование</t>
+  </si>
+  <si>
+    <t>новый класс берет поля и методы родителя</t>
+  </si>
+  <si>
+    <t>Smartphone наследует CellPhone, тот WirelessPhone, тот AbstractPhone</t>
+  </si>
+  <si>
+    <t>скрыть внутреннюю реализацию, дать доступ через методы</t>
+  </si>
+  <si>
+    <t>поля year и company приватны, наружу открыты call() и ring()</t>
+  </si>
+  <si>
+    <t>Полиморфизм</t>
+  </si>
+  <si>
+    <t>общий интерфейс, а поведение зависит от типа</t>
+  </si>
+  <si>
+    <t>callAnotherUser(AbstractPhone) работает с любой моделью телефона</t>
+  </si>
+  <si>
+    <t>Абстракция означает выделение главных, наиболее значимых характеристик предмета и, наоборот, отбрасывание второстепенных, незначительных.</t>
+  </si>
+  <si>
+    <t>Наследование это механизм, который позволяет описать новый класс на основе существующего (родительского). При этом свойства и функциональность родительского класса заимствуются новым классом.</t>
+  </si>
+  <si>
+    <t>Если у всех типов автомобилей есть 10 общих полей и 5 одинаковых методов, тебе достаточно вынести их в родительский класс Auto.</t>
+  </si>
+  <si>
+    <t>У тебя есть имя и фамилия. Их знают все твои знакомые. Но у них нет доступа к изменению твоего имени и фамилии. Этот процесс, можно сказать, «инкапсулирован» в паспортном столе: поменять имя фамилию можно только там, и сделать это можешь только ты.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">В мире Java состояние будущих объектов описывается в классе с помощью полей, а их поведение с помощью методов. Возможность же изменения состояния и поведения осуществляется с помощью модификаторов доступа к полям и методам: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>private, protected, public, а также default</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (доступ по умолчанию).</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Создадим класс Animal с единственным методом voice() и двух его наследников, Cat и Dog.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       Animal dog = new Dog();
+       dog.voice();
+Мы создали ссылку Animal, но объект ведет себя как Dog. При необходимости он может вести себя как кошка, лошадь или другое животное. Главное это присвоить ссылке общего типа Animal объект конкретного класса-наследника.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Как правило, концепция </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>полиморфизма</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> часто выражается фразой "один
+интерфейс, несколько методов': Это означает возможность разработки общеrо
+интерфейса для rруппы связанных действий, что поможет уменьшить
+сложность, позволив использовать один и тот же интерфейс для указания
+общего класса действий. Задачей компилятора будет выбор конкретноrо действия
+(т.е. метода) применительно к каждой ситуации. Вам, как проrраммисту,
+не придется делать такой выбор вручную. Вам понадобится только запомнить
+и задействовать общий интерфейс.
+Продолжая аналоrию с собаками, можно отметить, что обоняние собаки
+полиморфно. Если собака почует кошку, то она залает и побежит за ней. Если
+собака почувствует запах еды, тоrда у нее начнется слюноотделение, и она побежит
+к миске. В обеих ситуациях работает одно и то же обоняние. Разница
+в том, что именно издает запах, т.е. тип данных, с которыми имеет дело собачий
+нос! Та же общая концепция может быть реализована в Java, поскольку
+она применяется к методам внутри проrраммы Java.</t>
+    </r>
+  </si>
+  <si>
+    <t>Чтобы распаковать объект, нужно просто присвоить ссылку на него переменной
+примитивного типа. Например, для распаковки iOb можно использовать
+такую строку:</t>
+  </si>
+  <si>
+    <t>i n t i = iOb ;</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Благодаря </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>автоупаковке</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> устраняется потребность в ручном создании объекта
+с целью помещения в него значения примитивного типа. Понадобится
+лишь присвоить это значение ссылке на оболочку типа, а компилятор Java
+самостоятельно создаст объект. Скажем, вот современный способ создания
+объекта Integer со значением 1 0 0:</t>
+    </r>
+  </si>
+  <si>
+    <t>Integer iOb = 1 0 0 ; / / ав тоупаков ка значения int</t>
+  </si>
+  <si>
+    <t>Данный оператор инкрементирует значение в iOb. О н работает так: объект
+iOb распаковывается, значение инкрементируется, а результат повторно
+упаковывается.</t>
+  </si>
+  <si>
+    <t>`+ + i Ob ;</t>
+  </si>
+  <si>
+    <t>I nteger iOb = 2 ;
+swi tch ( iOb ) {
+case 1 :
+System . out . println ( "oдин " ) ;
+brea k ;
+case 2 :
+System . out . printl n ( "двa " ) ;
+b rea k ;
+defau l t :
+Sys tem . out . println ( "oшибкa " ) ;
+}</t>
+  </si>
+  <si>
+    <t>Благодаря автораспаковке числовые объекты I nteger можно использовать
+для управления оператором swi tch.</t>
+  </si>
+  <si>
+    <t>приведенном примере объекты типа DouЫe со держат значения, применяемые
+для вычисления гипотенузы прямоугол ьного треугольника. Хотя
+формал ьно этот код корректен и действительно работает правиль но, он демонстрирует
+крайне неудачное использование автоупаковки/автораспаковки.
+Он гораздо менее эффективен, чем эквивалентный код, написанный с применением
+примитивного типа douЫe. Дело в том, что каждая автоупаковка и
+автораспаковка добавляют накладные расходы, которые отсутствуют в случае
+использования примитивного типа.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">// </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Неудачное применение</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ав тоупаковки/а втораспаковки !
+DouЫe а , Ь , с ;
+а = 1 0 . 0 ;
+Ь = 4 . 0 ;
+с = Math . sqrt ( а * а + Ь * Ь ) ;
+System . out . print l n ( " Гиnoтeнyзa равна " + с ) ;</t>
+    </r>
+  </si>
+  <si>
+    <t>Автоупаковка</t>
+  </si>
+  <si>
+    <t>В классе NurnЬer объявлены методы, которые
+возвращают значение объекта в каждом из различных числовых форматов</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">byte </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>byteValue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ( )
+douЫ e </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>douЬleValue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ( )
+float </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>floatValue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ( )
+int </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intValue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ( )
+long </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>longValue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ( )
+short s </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>hortValue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ( )</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">В настоящее время для пол учения
+объекта оболочки настоятельно рекомендуется использовать один из методов
+va lueO f ( ) .
+Метод valueOf ( ) является стати ческим членом всех классов
+оболочек числовых типов и все числовые классы поддерживают формы, которые преобразуют </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>числовое значение ил и его строковое представление</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> в
+объект.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Во всех оболочках числовых типов определены конструкторы, которые позволяют
+создавать объект из </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>заданного значения или строкового представления</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+этого значения.</t>
+    </r>
+  </si>
+  <si>
+    <t>Не рекомендуется, тк устарело</t>
+  </si>
+  <si>
+    <t>Integer ( i nt num )
+Integer ( String str )</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">static Integer </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>valueOf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ( int va l )
+static Integer </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>valueOf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ( S t ri ng val S t r ) throws NumЬerFormatExcept ion
+Integer iOb = Integer . </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>valueOf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ( l 0 0 ) ;</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>int = Integer.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>intValue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Integer =  Integer . </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>valueOf</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <t>Оболочки числовых типов</t>
+  </si>
+  <si>
+    <t>Класс Boolean</t>
+  </si>
+  <si>
+    <t>Boolean ( boolean boolVal ue)
+Boolean ( S tring boolString )</t>
+  </si>
+  <si>
+    <r>
+      <t>В первой верси и конструктора аргумент boo l Va lue дол жен быть л ибо
+t rue, либо fa lse. 
+Что касается второй версии конструктора, есл и арг умент
+boo lString содержит строку</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>true</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> "</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (в верхнем или нижнем регистре), тогда
+новый объект Boo lean будет хранить з начение</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> t rue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, а и наче - fa lse.</t>
+    </r>
+  </si>
+  <si>
+    <t>static Boolean valueOf ( boolean boolValue )
+static Boolean valueOf ( S tring boolString)</t>
+  </si>
+  <si>
+    <t>Класс Character</t>
+  </si>
+  <si>
+    <t>Characte r ( char ch )</t>
+  </si>
+  <si>
+    <t>В аргументе ch указ ывается символ, который будет помещен в оболочк у
+создаваемого объекта Character.</t>
+  </si>
+  <si>
+    <t>Метод va lueOf () возвращает объект Cha racter, содержащий внутри себя
+символ из ch.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Чтобы получить значение char, хранящееся в объекте Character, необходимо
+выз вать метод cha rValue () </t>
+  </si>
+  <si>
+    <t>char charValue ( )</t>
+  </si>
+  <si>
+    <t>static Character valueOf ( cha r символ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int number = Integer.parseInt( str ) //321
+int number = Integer.parseInt("321") //321
+int number = Integer.parseInt("321" + 0) //3210
+</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> Integer.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>parseInt</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <t>тоже самое только лучше</t>
+  </si>
+  <si>
+    <t>Строки</t>
+  </si>
+  <si>
+    <r>
+      <t>String.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>toLowerCase</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>String name = "Rom"
+String name2 = name.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>toLowerCase</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(); //rom</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>String.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>toUpperCase</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>String name = "Rom"
+String name2 = name.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>toUpperCase</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(); //ROM</t>
+    </r>
+  </si>
+  <si>
+    <t>Считывание с клавиатуры</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="39" x14ac:knownFonts="1">
+  <fonts count="49" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -10180,8 +11979,79 @@
       <charset val="204"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF151F33"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF151F33"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF151F33"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -10221,6 +12091,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0FF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -10396,9 +12278,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -10409,23 +12291,23 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="29" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="30" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -10473,10 +12355,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="27" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="28" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="28" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="29" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -10506,82 +12388,88 @@
     <xf numFmtId="49" fontId="0" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="27" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="26" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="35" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="49" fontId="25" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="24" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="23" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="22" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="21" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="20" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -10590,49 +12478,46 @@
     <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="16" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="15" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="17" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="6" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="15" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -10644,73 +12529,70 @@
     <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="11" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="4" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="38" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="10" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="10" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="30" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="30" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="37" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10719,13 +12601,13 @@
     <xf numFmtId="49" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="34" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="35" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10734,80 +12616,59 @@
     <xf numFmtId="49" fontId="0" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="21" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="22" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="32" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="32" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="31" fillId="4" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="31" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="29" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -10815,11 +12676,33 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="41" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12560,6 +14443,55 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>362856</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>52195</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>2755509</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1016000</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Рисунок 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3352157-5F52-A868-A91F-733E213B96E7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11375570" y="6855766"/>
+          <a:ext cx="2392653" cy="963805"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -13063,7 +14995,7 @@
       </c>
       <c r="D21" s="22"/>
     </row>
-    <row r="22" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A22" s="21" t="s">
         <v>16</v>
       </c>
@@ -13075,7 +15007,7 @@
       </c>
       <c r="D22" s="22"/>
     </row>
-    <row r="23" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A23" s="21" t="s">
         <v>17</v>
       </c>
@@ -13087,7 +15019,7 @@
       </c>
       <c r="D23" s="22"/>
     </row>
-    <row r="24" spans="1:4" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A24" s="23" t="s">
         <v>27</v>
       </c>
@@ -13185,7 +15117,7 @@
       </c>
       <c r="D33" s="14"/>
     </row>
-    <row r="34" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A34" s="13" t="s">
         <v>46</v>
       </c>
@@ -13223,7 +15155,7 @@
       <c r="C37" s="11"/>
       <c r="D37" s="12"/>
     </row>
-    <row r="38" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:4" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="29" t="s">
         <v>34</v>
       </c>
@@ -13323,7 +15255,7 @@
       </c>
       <c r="D46" s="22"/>
     </row>
-    <row r="47" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" s="32"/>
       <c r="C47" s="2" t="s">
         <v>60</v>
@@ -13483,7 +15415,7 @@
       </c>
       <c r="D61" s="22"/>
     </row>
-    <row r="62" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62" s="32"/>
       <c r="C62" s="2" t="s">
         <v>106</v>
@@ -13515,7 +15447,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="66" spans="1:22" ht="87" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A66" s="32"/>
       <c r="C66" s="10" t="s">
         <v>110</v>
@@ -13587,7 +15519,7 @@
       </c>
       <c r="D73" s="22"/>
     </row>
-    <row r="74" spans="1:22" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:22" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="23" t="s">
         <v>133</v>
       </c>
@@ -13644,7 +15576,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" ht="58" x14ac:dyDescent="0.35">
       <c r="B82" s="2" t="s">
         <v>155</v>
       </c>
@@ -13685,12 +15617,12 @@
         <v>145</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="58" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="C86" s="46" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
       <c r="C87" s="46" t="s">
         <v>142</v>
       </c>
@@ -13709,7 +15641,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:7" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="C89" s="48" t="s">
         <v>158</v>
       </c>
@@ -13817,7 +15749,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="100" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:22" ht="116" x14ac:dyDescent="0.35">
       <c r="A100" s="1" t="s">
         <v>186</v>
       </c>
@@ -13852,7 +15784,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="104" spans="1:22" ht="232" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:22" ht="203" x14ac:dyDescent="0.35">
       <c r="B104" s="42" t="s">
         <v>230</v>
       </c>
@@ -13880,7 +15812,7 @@
       </c>
       <c r="C106" s="53"/>
     </row>
-    <row r="107" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A107" s="1" t="s">
         <v>195</v>
       </c>
@@ -13914,7 +15846,7 @@
       <c r="C110" s="116" t="s">
         <v>924</v>
       </c>
-      <c r="D110" s="140"/>
+      <c r="D110" s="133"/>
     </row>
     <row r="111" spans="1:22" x14ac:dyDescent="0.35">
       <c r="C111" s="53"/>
@@ -13965,7 +15897,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="117" spans="1:22" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:22" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A117" s="2" t="s">
         <v>209</v>
       </c>
@@ -14006,7 +15938,7 @@
       </c>
       <c r="D121" s="22"/>
     </row>
-    <row r="122" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A122" s="32" t="s">
         <v>217</v>
       </c>
@@ -14037,7 +15969,7 @@
       </c>
       <c r="D125" s="22"/>
     </row>
-    <row r="126" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A126" s="21"/>
       <c r="C126" s="53" t="s">
         <v>224</v>
@@ -14228,7 +16160,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="149" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:22" ht="58" x14ac:dyDescent="0.35">
       <c r="A149" s="57"/>
       <c r="C149" s="57" t="s">
         <v>255</v>
@@ -14239,7 +16171,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="151" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="C151" s="57" t="s">
         <v>257</v>
       </c>
@@ -14247,7 +16179,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="152" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="C152" s="57" t="s">
         <v>258</v>
       </c>
@@ -14261,7 +16193,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="154" spans="1:22" ht="116" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:22" ht="101.5" x14ac:dyDescent="0.35">
       <c r="C154" s="57" t="s">
         <v>260</v>
       </c>
@@ -14596,7 +16528,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="203" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:22" ht="58" x14ac:dyDescent="0.35">
       <c r="C203" s="57" t="s">
         <v>322</v>
       </c>
@@ -14632,12 +16564,12 @@
         <v>325</v>
       </c>
     </row>
-    <row r="209" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="C209" s="57" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="210" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A210" s="1" t="s">
         <v>327</v>
       </c>
@@ -14709,7 +16641,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="217" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A217" s="1" t="s">
         <v>380</v>
       </c>
@@ -14720,7 +16652,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="218" spans="1:22" ht="116" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:22" ht="87" x14ac:dyDescent="0.35">
       <c r="B218" s="61" t="s">
         <v>384</v>
       </c>
@@ -14739,7 +16671,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="220" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:22" ht="116" x14ac:dyDescent="0.35">
       <c r="C220" s="64" t="s">
         <v>389</v>
       </c>
@@ -14784,14 +16716,14 @@
         <v>331</v>
       </c>
     </row>
-    <row r="226" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A226" s="21"/>
       <c r="C226" s="57" t="s">
         <v>332</v>
       </c>
       <c r="D226" s="22"/>
     </row>
-    <row r="227" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A227" s="21"/>
       <c r="B227" s="2" t="s">
         <v>109</v>
@@ -14881,7 +16813,7 @@
       </c>
       <c r="D237" s="22"/>
     </row>
-    <row r="238" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A238" s="21" t="s">
         <v>347</v>
       </c>
@@ -15020,7 +16952,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="256" spans="1:22" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:22" ht="87" x14ac:dyDescent="0.35">
       <c r="C256" s="64" t="s">
         <v>391</v>
       </c>
@@ -15097,7 +17029,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="266" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:22" ht="58" x14ac:dyDescent="0.35">
       <c r="C266" s="64" t="s">
         <v>404</v>
       </c>
@@ -15107,7 +17039,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="268" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:22" ht="116" x14ac:dyDescent="0.35">
       <c r="B268" s="64" t="s">
         <v>421</v>
       </c>
@@ -15115,7 +17047,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="269" spans="1:22" ht="116" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:22" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A269" s="1" t="s">
         <v>405</v>
       </c>
@@ -15142,7 +17074,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="273" spans="1:22" ht="87" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="C273" s="64" t="s">
         <v>409</v>
       </c>
@@ -15166,7 +17098,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="276" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A276" s="1" t="s">
         <v>412</v>
       </c>
@@ -15177,7 +17109,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="277" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A277" s="1" t="s">
         <v>413</v>
       </c>
@@ -15242,7 +17174,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="284" spans="1:22" ht="145" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:22" ht="130.5" x14ac:dyDescent="0.35">
       <c r="C284" s="64" t="s">
         <v>429</v>
       </c>
@@ -15295,7 +17227,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="291" spans="1:4" ht="217.5" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:4" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A291" s="1" t="s">
         <v>441</v>
       </c>
@@ -15321,7 +17253,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="295" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="C295" s="66" t="s">
         <v>446</v>
       </c>
@@ -15350,12 +17282,12 @@
         <v>452</v>
       </c>
     </row>
-    <row r="299" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="C299" s="66" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="300" spans="1:4" ht="145" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
       <c r="C300" s="66" t="s">
         <v>455</v>
       </c>
@@ -15363,7 +17295,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="301" spans="1:4" ht="116" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
       <c r="C301" s="66" t="s">
         <v>456</v>
       </c>
@@ -15414,7 +17346,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="312" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="A312" s="21"/>
       <c r="C312" s="69" t="s">
         <v>464</v>
@@ -15629,7 +17561,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="336" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A336" s="21"/>
       <c r="C336" s="82" t="s">
         <v>651</v>
@@ -15651,7 +17583,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="339" spans="1:4" ht="116" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A339" s="21" t="s">
         <v>636</v>
       </c>
@@ -15691,14 +17623,14 @@
       </c>
       <c r="D342" s="22"/>
     </row>
-    <row r="343" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A343" s="21"/>
       <c r="C343" s="67" t="s">
         <v>507</v>
       </c>
       <c r="D343" s="22"/>
     </row>
-    <row r="344" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A344" s="21" t="s">
         <v>508</v>
       </c>
@@ -15721,7 +17653,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="346" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A346" s="21"/>
       <c r="C346" s="67" t="s">
         <v>519</v>
@@ -15738,7 +17670,7 @@
       </c>
       <c r="D347" s="22"/>
     </row>
-    <row r="348" spans="1:4" ht="174" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
       <c r="A348" s="21" t="s">
         <v>517</v>
       </c>
@@ -15780,7 +17712,7 @@
       </c>
       <c r="D351" s="22"/>
     </row>
-    <row r="352" spans="1:4" ht="73" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="352" spans="1:4" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A352" s="23" t="s">
         <v>529</v>
       </c>
@@ -15800,7 +17732,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="355" spans="1:22" ht="377" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:22" ht="362.5" x14ac:dyDescent="0.35">
       <c r="A355" s="1" t="s">
         <v>533</v>
       </c>
@@ -15843,7 +17775,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="360" spans="1:22" ht="29" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A360" s="1" t="s">
         <v>538</v>
       </c>
@@ -15851,7 +17783,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="361" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:22" ht="29" x14ac:dyDescent="0.35">
       <c r="C361" s="73" t="s">
         <v>539</v>
       </c>
@@ -15914,7 +17846,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="368" spans="1:22" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:22" ht="217.5" x14ac:dyDescent="0.35">
       <c r="A368" s="73" t="s">
         <v>553</v>
       </c>
@@ -16090,7 +18022,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="386" spans="1:4" ht="145" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:4" ht="116" x14ac:dyDescent="0.35">
       <c r="A386" s="21"/>
       <c r="B386" s="73" t="s">
         <v>584</v>
@@ -16100,7 +18032,7 @@
       </c>
       <c r="D386" s="22"/>
     </row>
-    <row r="387" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A387" s="21"/>
       <c r="B387" s="73"/>
       <c r="C387" s="73" t="s">
@@ -16108,7 +18040,7 @@
       </c>
       <c r="D387" s="22"/>
     </row>
-    <row r="388" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A388" s="21"/>
       <c r="B388" s="73"/>
       <c r="C388" s="73" t="s">
@@ -16213,7 +18145,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="400" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:4" ht="58" x14ac:dyDescent="0.35">
       <c r="A400" s="21"/>
       <c r="B400" s="73" t="s">
         <v>607</v>
@@ -16246,7 +18178,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="404" spans="1:21" ht="29" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:21" x14ac:dyDescent="0.35">
       <c r="C404" s="73" t="s">
         <v>615</v>
       </c>
@@ -16283,7 +18215,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="409" spans="1:21" ht="87" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:21" ht="72.5" x14ac:dyDescent="0.35">
       <c r="C409" s="73" t="s">
         <v>624</v>
       </c>
@@ -16443,7 +18375,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="426" spans="1:22" ht="246.5" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:22" ht="232" x14ac:dyDescent="0.35">
       <c r="C426" s="80" t="s">
         <v>647</v>
       </c>
@@ -16481,7 +18413,7 @@
       <c r="U429" s="1"/>
       <c r="V429" s="2"/>
     </row>
-    <row r="430" spans="1:22" ht="87" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A430" s="18" t="s">
         <v>654</v>
       </c>
@@ -16493,7 +18425,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="431" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:22" ht="58" x14ac:dyDescent="0.35">
       <c r="A431" s="21" t="s">
         <v>657</v>
       </c>
@@ -16505,7 +18437,7 @@
       </c>
       <c r="D431" s="22"/>
     </row>
-    <row r="432" spans="1:22" ht="174.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="432" spans="1:22" ht="160" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A432" s="33" t="s">
         <v>661</v>
       </c>
@@ -16540,7 +18472,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="435" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A435" s="32" t="s">
         <v>669</v>
       </c>
@@ -16554,7 +18486,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="436" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A436" s="21" t="s">
         <v>672</v>
       </c>
@@ -16589,7 +18521,7 @@
       </c>
       <c r="D438" s="25"/>
     </row>
-    <row r="439" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A439" s="18" t="s">
         <v>680</v>
       </c>
@@ -16609,7 +18541,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="441" spans="1:4" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:4" ht="116" x14ac:dyDescent="0.35">
       <c r="A441" s="21" t="s">
         <v>687</v>
       </c>
@@ -16618,7 +18550,7 @@
       </c>
       <c r="D441" s="22"/>
     </row>
-    <row r="442" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A442" s="21" t="s">
         <v>688</v>
       </c>
@@ -16627,7 +18559,7 @@
       </c>
       <c r="D442" s="22"/>
     </row>
-    <row r="443" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A443" s="32" t="s">
         <v>689</v>
       </c>
@@ -16638,7 +18570,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="444" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A444" s="21"/>
       <c r="B444" s="2" t="s">
         <v>713</v>
@@ -16673,7 +18605,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="448" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A448" s="21" t="s">
         <v>698</v>
       </c>
@@ -16682,14 +18614,14 @@
       </c>
       <c r="D448" s="22"/>
     </row>
-    <row r="449" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A449" s="21"/>
       <c r="C449" s="83" t="s">
         <v>697</v>
       </c>
       <c r="D449" s="22"/>
     </row>
-    <row r="450" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A450" s="21" t="s">
         <v>699</v>
       </c>
@@ -16737,7 +18669,7 @@
       </c>
       <c r="D454" s="22"/>
     </row>
-    <row r="455" spans="1:22" ht="102" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="455" spans="1:22" ht="87.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A455" s="23" t="s">
         <v>713</v>
       </c>
@@ -16803,7 +18735,7 @@
       </c>
       <c r="D460" s="22"/>
     </row>
-    <row r="461" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A461" s="21"/>
       <c r="C461" s="83" t="s">
         <v>723</v>
@@ -16817,7 +18749,7 @@
       </c>
       <c r="D462" s="22"/>
     </row>
-    <row r="463" spans="1:22" ht="101.5" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:22" ht="87" x14ac:dyDescent="0.35">
       <c r="A463" s="21" t="s">
         <v>725</v>
       </c>
@@ -16831,21 +18763,21 @@
         <v>726</v>
       </c>
     </row>
-    <row r="464" spans="1:22" ht="159.5" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:22" ht="116" x14ac:dyDescent="0.35">
       <c r="A464" s="21"/>
       <c r="C464" s="83" t="s">
         <v>729</v>
       </c>
       <c r="D464" s="22"/>
     </row>
-    <row r="465" spans="1:22" ht="116" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:22" ht="87" x14ac:dyDescent="0.35">
       <c r="A465" s="21"/>
       <c r="C465" s="83" t="s">
         <v>730</v>
       </c>
       <c r="D465" s="22"/>
     </row>
-    <row r="466" spans="1:22" ht="58.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="466" spans="1:22" ht="44" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A466" s="23"/>
       <c r="B466" s="24"/>
       <c r="C466" s="86" t="s">
@@ -16863,7 +18795,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="468" spans="1:22" ht="87" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:22" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A468" s="21" t="s">
         <v>737</v>
       </c>
@@ -16896,7 +18828,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="471" spans="1:22" ht="58" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A471" s="21"/>
       <c r="C471" s="83" t="s">
         <v>742</v>
@@ -17204,13 +19136,13 @@
       </c>
     </row>
     <row r="502" spans="1:4" ht="29" x14ac:dyDescent="0.35">
-      <c r="A502" s="119" t="s">
+      <c r="A502" s="117" t="s">
         <v>911</v>
       </c>
-      <c r="B502" s="120" t="s">
+      <c r="B502" s="118" t="s">
         <v>902</v>
       </c>
-      <c r="C502" s="118" t="s">
+      <c r="C502" s="116" t="s">
         <v>900</v>
       </c>
       <c r="D502" s="22"/>
@@ -17331,7 +19263,7 @@
       </c>
       <c r="D514" s="22"/>
     </row>
-    <row r="515" spans="1:21" ht="29" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A515" s="92"/>
       <c r="B515" s="89"/>
       <c r="C515" s="93" t="s">
@@ -17670,7 +19602,7 @@
       <c r="A543" s="1" t="s">
         <v>912</v>
       </c>
-      <c r="C543" s="122" t="s">
+      <c r="C543" s="120" t="s">
         <v>913</v>
       </c>
       <c r="P543" s="1"/>
@@ -17678,13 +19610,13 @@
       <c r="V543" s="2"/>
     </row>
     <row r="544" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A544" s="124" t="s">
+      <c r="A544" s="122" t="s">
         <v>917</v>
       </c>
       <c r="B544" s="11" t="s">
         <v>914</v>
       </c>
-      <c r="C544" s="125"/>
+      <c r="C544" s="123"/>
       <c r="D544" s="12" t="s">
         <v>860</v>
       </c>
@@ -17694,56 +19626,55 @@
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A545" s="13"/>
-      <c r="B545" s="126" t="s">
+      <c r="B545" s="54" t="s">
         <v>109</v>
       </c>
-      <c r="C545" s="127"/>
       <c r="D545" s="14"/>
     </row>
     <row r="546" spans="1:4" ht="188.5" x14ac:dyDescent="0.35">
-      <c r="A546" s="128" t="s">
+      <c r="A546" s="124" t="s">
         <v>907</v>
       </c>
-      <c r="B546" s="117" t="s">
+      <c r="B546" s="2" t="s">
         <v>910</v>
       </c>
-      <c r="C546" s="118" t="s">
+      <c r="C546" s="116" t="s">
         <v>862</v>
       </c>
       <c r="D546" s="14"/>
     </row>
     <row r="547" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A547" s="129" t="s">
+      <c r="A547" s="125" t="s">
         <v>916</v>
       </c>
-      <c r="B547" s="117" t="s">
+      <c r="B547" s="2" t="s">
         <v>915</v>
       </c>
-      <c r="C547" s="117" t="s">
+      <c r="C547" s="2" t="s">
         <v>905</v>
       </c>
       <c r="D547" s="14"/>
     </row>
     <row r="548" spans="1:4" ht="174" x14ac:dyDescent="0.35">
-      <c r="A548" s="130" t="s">
+      <c r="A548" s="126" t="s">
         <v>908</v>
       </c>
-      <c r="B548" s="118" t="s">
+      <c r="B548" s="116" t="s">
         <v>909</v>
       </c>
-      <c r="C548" s="118" t="s">
+      <c r="C548" s="116" t="s">
         <v>906</v>
       </c>
       <c r="D548" s="14"/>
     </row>
     <row r="549" spans="1:4" ht="72.5" x14ac:dyDescent="0.35">
-      <c r="A549" s="121" t="s">
+      <c r="A549" s="119" t="s">
         <v>919</v>
       </c>
       <c r="B549" s="2" t="s">
         <v>931</v>
       </c>
-      <c r="C549" s="123" t="s">
+      <c r="C549" s="121" t="s">
         <v>932</v>
       </c>
       <c r="D549" s="1" t="s">
@@ -17768,8 +19699,7 @@
       <c r="A551" s="30" t="s">
         <v>863</v>
       </c>
-      <c r="B551" s="117"/>
-      <c r="C551" s="131" t="s">
+      <c r="C551" s="127" t="s">
         <v>896</v>
       </c>
       <c r="D551" s="14" t="s">
@@ -17780,36 +19710,34 @@
       <c r="A552" s="13" t="s">
         <v>865</v>
       </c>
-      <c r="B552" s="117"/>
-      <c r="C552" s="118" t="s">
+      <c r="C552" s="116" t="s">
         <v>925</v>
       </c>
       <c r="D552" s="14"/>
     </row>
     <row r="553" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A553" s="13"/>
-      <c r="B553" s="132" t="s">
+      <c r="B553" s="103" t="s">
         <v>869</v>
       </c>
-      <c r="C553" s="118" t="s">
+      <c r="C553" s="116" t="s">
         <v>899</v>
       </c>
       <c r="D553" s="14"/>
     </row>
-    <row r="554" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:4" ht="29" x14ac:dyDescent="0.35">
       <c r="A554" s="13"/>
-      <c r="B554" s="117"/>
-      <c r="C554" s="118" t="s">
+      <c r="C554" s="116" t="s">
         <v>898</v>
       </c>
       <c r="D554" s="14"/>
     </row>
     <row r="555" spans="1:4" ht="58" x14ac:dyDescent="0.35">
-      <c r="A555" s="124" t="s">
+      <c r="A555" s="122" t="s">
         <v>922</v>
       </c>
       <c r="B555" s="11"/>
-      <c r="C555" s="141" t="s">
+      <c r="C555" s="123" t="s">
         <v>926</v>
       </c>
       <c r="D555" s="12" t="s">
@@ -17817,13 +19745,13 @@
       </c>
     </row>
     <row r="556" spans="1:4" ht="232" x14ac:dyDescent="0.35">
-      <c r="A556" s="128" t="s">
+      <c r="A556" s="124" t="s">
         <v>923</v>
       </c>
-      <c r="B556" s="117" t="s">
+      <c r="B556" s="2" t="s">
         <v>927</v>
       </c>
-      <c r="C556" s="118" t="s">
+      <c r="C556" s="116" t="s">
         <v>866</v>
       </c>
       <c r="D556" s="14"/>
@@ -17832,10 +19760,10 @@
       <c r="A557" s="13" t="s">
         <v>933</v>
       </c>
-      <c r="B557" s="117" t="s">
+      <c r="B557" s="2" t="s">
         <v>934</v>
       </c>
-      <c r="C557" s="118" t="s">
+      <c r="C557" s="116" t="s">
         <v>935</v>
       </c>
       <c r="D557" s="14"/>
@@ -17847,17 +19775,15 @@
       <c r="B558" s="16" t="s">
         <v>937</v>
       </c>
-      <c r="C558" s="133" t="s">
+      <c r="C558" s="128" t="s">
         <v>938</v>
       </c>
       <c r="D558" s="17"/>
     </row>
     <row r="559" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A559" s="129" t="s">
+      <c r="A559" s="125" t="s">
         <v>918</v>
       </c>
-      <c r="B559" s="117"/>
-      <c r="C559" s="127"/>
       <c r="D559" s="14" t="s">
         <v>868</v>
       </c>
@@ -17866,20 +19792,19 @@
       <c r="A560" s="13" t="s">
         <v>872</v>
       </c>
-      <c r="B560" s="117"/>
-      <c r="C560" s="118" t="s">
+      <c r="C560" s="116" t="s">
         <v>870</v>
       </c>
       <c r="D560" s="14"/>
     </row>
     <row r="561" spans="1:4" ht="145" x14ac:dyDescent="0.35">
-      <c r="A561" s="135" t="s">
+      <c r="A561" s="130" t="s">
         <v>881</v>
       </c>
-      <c r="B561" s="117" t="s">
+      <c r="B561" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="C561" s="136" t="s">
+      <c r="C561" s="105" t="s">
         <v>889</v>
       </c>
       <c r="D561" s="14" t="s">
@@ -17887,33 +19812,32 @@
       </c>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A562" s="135"/>
-      <c r="B562" s="117"/>
-      <c r="C562" s="137" t="s">
+      <c r="A562" s="130"/>
+      <c r="C562" s="47" t="s">
         <v>888</v>
       </c>
-      <c r="D562" s="138" t="s">
+      <c r="D562" s="131" t="s">
         <v>887</v>
       </c>
     </row>
     <row r="563" spans="1:4" ht="159.5" x14ac:dyDescent="0.35">
-      <c r="A563" s="135" t="s">
+      <c r="A563" s="130" t="s">
         <v>882</v>
       </c>
-      <c r="B563" s="117" t="s">
+      <c r="B563" s="2" t="s">
         <v>884</v>
       </c>
-      <c r="C563" s="136" t="s">
+      <c r="C563" s="105" t="s">
         <v>885</v>
       </c>
-      <c r="D563" s="139" t="s">
+      <c r="D563" s="132" t="s">
         <v>886</v>
       </c>
     </row>
     <row r="564" spans="1:4" ht="87" x14ac:dyDescent="0.35">
       <c r="A564" s="15"/>
       <c r="B564" s="16"/>
-      <c r="C564" s="134" t="s">
+      <c r="C564" s="129" t="s">
         <v>871</v>
       </c>
       <c r="D564" s="17"/>
@@ -17971,7 +19895,7 @@
       <c r="V579" s="2"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="30" type="noConversion"/>
+  <phoneticPr fontId="31" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="G92" r:id="rId1" xr:uid="{58F83308-1CDC-4543-BEF2-348F3724C1F0}"/>
     <hyperlink ref="G93" r:id="rId2" xr:uid="{42142E19-2E01-403A-8F5F-3E5AAC87B996}"/>
@@ -17981,4 +19905,1120 @@
   <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId4"/>
   <drawing r:id="rId5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F519FFA-AD0F-4F27-89DD-3EDF4FD008EA}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:U69"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.54296875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.1796875" style="135" customWidth="1"/>
+    <col min="4" max="4" width="56.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.26953125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.08984375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.90625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.36328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.81640625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.90625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6328125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.90625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.81640625" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.81640625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.7265625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.90625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.1796875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7265625" style="8"/>
+    <col min="21" max="21" width="67.7265625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.36328125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.36328125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6328125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.453125" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.26953125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.7265625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="C1" s="135" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A2" s="3"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A3" s="47" t="s">
+        <v>941</v>
+      </c>
+      <c r="B3" s="37"/>
+      <c r="D3" s="1" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A4" s="136" t="s">
+        <v>960</v>
+      </c>
+      <c r="B4" s="136" t="s">
+        <v>961</v>
+      </c>
+      <c r="C4" s="136" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="137" t="s">
+        <v>963</v>
+      </c>
+      <c r="B5" s="138" t="s">
+        <v>964</v>
+      </c>
+      <c r="C5" s="138" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A6" s="137" t="s">
+        <v>943</v>
+      </c>
+      <c r="B6" s="138" t="s">
+        <v>966</v>
+      </c>
+      <c r="C6" s="138" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A7" s="137" t="s">
+        <v>954</v>
+      </c>
+      <c r="B7" s="138" t="s">
+        <v>968</v>
+      </c>
+      <c r="C7" s="138" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A8" s="137" t="s">
+        <v>970</v>
+      </c>
+      <c r="B8" s="138" t="s">
+        <v>971</v>
+      </c>
+      <c r="C8" s="138" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="B9" s="37"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A10" s="58" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="B11" s="2" t="s">
+        <v>944</v>
+      </c>
+      <c r="C11" s="135" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="290" x14ac:dyDescent="0.35">
+      <c r="B12" s="2" t="s">
+        <v>945</v>
+      </c>
+      <c r="C12" s="135" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A13" s="58" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B14" s="2" t="s">
+        <v>949</v>
+      </c>
+      <c r="C14" s="135" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="58" x14ac:dyDescent="0.35">
+      <c r="B15" s="2" t="s">
+        <v>951</v>
+      </c>
+      <c r="C15" s="135" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="87" x14ac:dyDescent="0.35">
+      <c r="C16" s="135" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B17" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="C17" s="135" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="58" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="C19" s="135" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="58" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="174" x14ac:dyDescent="0.35">
+      <c r="B21" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="C21" s="135" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B22" s="2" t="s">
+        <v>950</v>
+      </c>
+      <c r="C22" s="135" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="47" t="s">
+        <v>973</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="58" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+      <c r="B25" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="C25" s="135" t="s">
+        <v>975</v>
+      </c>
+      <c r="D25" s="135" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="139" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="C27" s="135" t="s">
+        <v>980</v>
+      </c>
+      <c r="D27" s="135" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="C28" s="135" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="A29" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="C29" s="135" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="136" t="s">
+        <v>986</v>
+      </c>
+      <c r="B30" s="136" t="s">
+        <v>987</v>
+      </c>
+      <c r="C30" s="136" t="s">
+        <v>988</v>
+      </c>
+      <c r="D30" s="136" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="137" t="s">
+        <v>990</v>
+      </c>
+      <c r="B31" s="138" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C31" s="138" t="s">
+        <v>991</v>
+      </c>
+      <c r="D31" s="138" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="137" t="s">
+        <v>993</v>
+      </c>
+      <c r="B32" s="138" t="s">
+        <v>999</v>
+      </c>
+      <c r="C32" s="138" t="s">
+        <v>994</v>
+      </c>
+      <c r="D32" s="138" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="23" x14ac:dyDescent="0.35">
+      <c r="A33" s="137" t="s">
+        <v>978</v>
+      </c>
+      <c r="B33" s="138" t="s">
+        <v>996</v>
+      </c>
+      <c r="C33" s="138" t="s">
+        <v>997</v>
+      </c>
+      <c r="D33" s="138" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="47" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="34.5" x14ac:dyDescent="0.35">
+      <c r="C36" s="140" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D36" s="141" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="46" x14ac:dyDescent="0.35">
+      <c r="B37" s="2" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C37" s="140" t="s">
+        <v>1003</v>
+      </c>
+      <c r="D37" s="141" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="87" x14ac:dyDescent="0.35">
+      <c r="B38" s="2" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C38" s="140" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="B39" s="2" t="s">
+        <v>1027</v>
+      </c>
+      <c r="C39" s="140" t="s">
+        <v>1005</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="212.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="2"/>
+      <c r="C40" s="2" t="s">
+        <v>1029</v>
+      </c>
+      <c r="D40" s="2"/>
+    </row>
+    <row r="41" spans="1:4" ht="23" x14ac:dyDescent="0.35">
+      <c r="C41" s="140" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="58" x14ac:dyDescent="0.35">
+      <c r="A42" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C42" s="135" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="136" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B43" s="136" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C43" s="136" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="138" t="s">
+        <v>461</v>
+      </c>
+      <c r="B44" s="138" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C44" s="138" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="138" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B45" s="138" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C45" s="138" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="138" t="s">
+        <v>462</v>
+      </c>
+      <c r="B46" s="138" t="s">
+        <v>1017</v>
+      </c>
+      <c r="C46" s="138" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="138" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B47" s="138" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C47" s="138" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A49" s="47" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="B50" s="2" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C50" s="135" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="B51" s="2" t="s">
+        <v>1031</v>
+      </c>
+      <c r="C51" s="135" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="B52" s="2" t="s">
+        <v>1035</v>
+      </c>
+      <c r="C52" s="135" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="B53" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C53" s="135" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="159.5" x14ac:dyDescent="0.35">
+      <c r="B54" s="135" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C54" s="135" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" s="58" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="87" x14ac:dyDescent="0.35">
+      <c r="A56" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C56" s="135" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A57" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C57" s="135" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="58" x14ac:dyDescent="0.35">
+      <c r="A58" s="142" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C58" s="135" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="116" x14ac:dyDescent="0.35">
+      <c r="A59" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C59" s="135" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" s="58" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A63" s="142" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C63" s="135" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="B64" s="2" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" s="58" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="B66" s="2" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C66" s="135" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="A67" s="142" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C67" s="135" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="29" x14ac:dyDescent="0.35">
+      <c r="B68" s="2" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C68" s="135" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" s="47" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C416D70-361B-4690-A2CE-22F2DB53B63A}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:U68"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="36" style="1" customWidth="1"/>
+    <col min="2" max="2" width="50.54296875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="71.1796875" style="135" customWidth="1"/>
+    <col min="4" max="4" width="56.453125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="6.26953125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="43.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="55.08984375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="67.90625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="64.36328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="7.81640625" style="7" customWidth="1"/>
+    <col min="11" max="11" width="39.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="48.90625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="72.6328125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="43.90625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.81640625" style="7" customWidth="1"/>
+    <col min="16" max="16" width="56.81640625" style="2" customWidth="1"/>
+    <col min="17" max="17" width="46.7265625" style="2" customWidth="1"/>
+    <col min="18" max="18" width="62.90625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="49.1796875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="8.7265625" style="8"/>
+    <col min="21" max="21" width="67.7265625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="68.36328125" style="1" customWidth="1"/>
+    <col min="23" max="24" width="59.36328125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="59.6328125" style="1" customWidth="1"/>
+    <col min="26" max="26" width="99.453125" style="1" customWidth="1"/>
+    <col min="27" max="27" width="41.26953125" style="1" customWidth="1"/>
+    <col min="28" max="16384" width="8.7265625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="C1" s="135" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A2" s="3"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="134"/>
+      <c r="D2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="P2" s="5"/>
+      <c r="Q2" s="5"/>
+      <c r="R2" s="5"/>
+      <c r="S2" s="5"/>
+      <c r="U2" s="5"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A3" s="47" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B3" s="37"/>
+    </row>
+    <row r="4" spans="1:21" ht="29" x14ac:dyDescent="0.35">
+      <c r="A4" s="135" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B4" s="135"/>
+      <c r="C4" s="135" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D4" s="135"/>
+    </row>
+    <row r="5" spans="1:21" ht="29" x14ac:dyDescent="0.35">
+      <c r="A5" s="135" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B5" s="135"/>
+      <c r="C5" s="135" t="s">
+        <v>1069</v>
+      </c>
+      <c r="D5" s="135"/>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A6" s="135"/>
+      <c r="B6" s="135"/>
+      <c r="D6" s="135"/>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A7" s="135"/>
+      <c r="B7" s="135"/>
+      <c r="D7" s="135"/>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A8" s="135"/>
+      <c r="B8" s="135"/>
+      <c r="D8" s="135"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A9" s="135"/>
+      <c r="B9" s="135"/>
+      <c r="D9" s="135"/>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A10" s="135"/>
+      <c r="B10" s="135"/>
+      <c r="D10" s="135"/>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A11" s="135"/>
+      <c r="B11" s="135"/>
+      <c r="D11" s="135"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A12" s="135"/>
+      <c r="B12" s="135"/>
+      <c r="D12" s="135"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A13" s="135"/>
+      <c r="B13" s="135"/>
+      <c r="D13" s="135"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A14" s="135"/>
+      <c r="B14" s="135"/>
+      <c r="D14" s="135"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A15" s="135"/>
+      <c r="B15" s="135"/>
+      <c r="D15" s="135"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A16" s="135"/>
+      <c r="B16" s="135"/>
+      <c r="D16" s="135"/>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="135"/>
+      <c r="B17" s="135"/>
+      <c r="D17" s="135"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="135"/>
+      <c r="B18" s="135"/>
+      <c r="D18" s="135"/>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="135"/>
+      <c r="B19" s="135"/>
+      <c r="D19" s="135"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="135"/>
+      <c r="B20" s="135"/>
+      <c r="D20" s="135"/>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="135"/>
+      <c r="B21" s="135"/>
+      <c r="D21" s="135"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="135"/>
+      <c r="B22" s="135"/>
+      <c r="D22" s="135"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="135"/>
+      <c r="B23" s="135"/>
+      <c r="D23" s="135"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="135"/>
+      <c r="B24" s="135"/>
+      <c r="D24" s="135"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="135"/>
+      <c r="B25" s="135"/>
+      <c r="D25" s="135"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="135"/>
+      <c r="B26" s="135"/>
+      <c r="D26" s="135"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="135"/>
+      <c r="B27" s="135"/>
+      <c r="D27" s="135"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="135"/>
+      <c r="B28" s="135"/>
+      <c r="D28" s="135"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="135"/>
+      <c r="B29" s="135"/>
+      <c r="D29" s="135"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="135"/>
+      <c r="B30" s="135"/>
+      <c r="D30" s="135"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="135"/>
+      <c r="B31" s="135"/>
+      <c r="D31" s="135"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="135"/>
+      <c r="B32" s="135"/>
+      <c r="D32" s="135"/>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A33" s="135"/>
+      <c r="B33" s="135"/>
+      <c r="D33" s="135"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A34" s="135"/>
+      <c r="B34" s="135"/>
+      <c r="D34" s="135"/>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A35" s="135"/>
+      <c r="B35" s="135"/>
+      <c r="D35" s="135"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A36" s="135"/>
+      <c r="B36" s="135"/>
+      <c r="D36" s="135"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A37" s="135"/>
+      <c r="B37" s="135"/>
+      <c r="D37" s="135"/>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A38" s="135"/>
+      <c r="B38" s="135"/>
+      <c r="D38" s="135"/>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A39" s="135"/>
+      <c r="B39" s="135"/>
+      <c r="D39" s="135"/>
+    </row>
+    <row r="40" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A40" s="135"/>
+      <c r="B40" s="135"/>
+      <c r="C40" s="135"/>
+      <c r="D40" s="135"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="1"/>
+      <c r="T40" s="8"/>
+      <c r="U40" s="2"/>
+    </row>
+    <row r="41" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="135"/>
+      <c r="B41" s="135"/>
+      <c r="C41" s="135"/>
+      <c r="D41" s="135"/>
+      <c r="F41" s="1"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="1"/>
+      <c r="I41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
+      <c r="M41" s="1"/>
+      <c r="N41" s="1"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="1"/>
+      <c r="T41" s="8"/>
+      <c r="U41" s="2"/>
+    </row>
+    <row r="42" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="135"/>
+      <c r="B42" s="135"/>
+      <c r="C42" s="135"/>
+      <c r="D42" s="135"/>
+      <c r="F42" s="1"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="1"/>
+      <c r="I42" s="1"/>
+      <c r="K42" s="1"/>
+      <c r="L42" s="1"/>
+      <c r="M42" s="1"/>
+      <c r="N42" s="1"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="1"/>
+      <c r="T42" s="8"/>
+      <c r="U42" s="2"/>
+    </row>
+    <row r="43" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="135"/>
+      <c r="B43" s="135"/>
+      <c r="C43" s="135"/>
+      <c r="D43" s="135"/>
+      <c r="F43" s="1"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="1"/>
+      <c r="I43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1"/>
+      <c r="N43" s="1"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="1"/>
+      <c r="T43" s="8"/>
+      <c r="U43" s="2"/>
+    </row>
+    <row r="44" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="135"/>
+      <c r="B44" s="135"/>
+      <c r="C44" s="135"/>
+      <c r="D44" s="135"/>
+      <c r="F44" s="1"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="1"/>
+      <c r="I44" s="1"/>
+      <c r="K44" s="1"/>
+      <c r="L44" s="1"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="8"/>
+      <c r="U44" s="2"/>
+    </row>
+    <row r="45" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="135"/>
+      <c r="B45" s="135"/>
+      <c r="C45" s="135"/>
+      <c r="D45" s="135"/>
+      <c r="F45" s="1"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="1"/>
+      <c r="I45" s="1"/>
+      <c r="K45" s="1"/>
+      <c r="L45" s="1"/>
+      <c r="M45" s="1"/>
+      <c r="N45" s="1"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="2"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="8"/>
+      <c r="U45" s="2"/>
+    </row>
+    <row r="46" spans="1:21" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="135"/>
+      <c r="B46" s="135"/>
+      <c r="C46" s="135"/>
+      <c r="D46" s="135"/>
+      <c r="F46" s="1"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="1"/>
+      <c r="I46" s="1"/>
+      <c r="K46" s="1"/>
+      <c r="L46" s="1"/>
+      <c r="M46" s="1"/>
+      <c r="N46" s="1"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="2"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="8"/>
+      <c r="U46" s="2"/>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A47" s="135"/>
+      <c r="B47" s="135"/>
+      <c r="D47" s="135"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A48" s="135"/>
+      <c r="B48" s="135"/>
+      <c r="D48" s="135"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="135"/>
+      <c r="B49" s="135"/>
+      <c r="D49" s="135"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="135"/>
+      <c r="B50" s="135"/>
+      <c r="D50" s="135"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="135"/>
+      <c r="B51" s="135"/>
+      <c r="D51" s="135"/>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="135"/>
+      <c r="B52" s="135"/>
+      <c r="D52" s="135"/>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="135"/>
+      <c r="B53" s="135"/>
+      <c r="D53" s="135"/>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="135"/>
+      <c r="B54" s="135"/>
+      <c r="D54" s="135"/>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="135"/>
+      <c r="B55" s="135"/>
+      <c r="D55" s="135"/>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="135"/>
+      <c r="B56" s="135"/>
+      <c r="D56" s="135"/>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="135"/>
+      <c r="B57" s="135"/>
+      <c r="D57" s="135"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="135"/>
+      <c r="B58" s="135"/>
+      <c r="D58" s="135"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="135"/>
+      <c r="B59" s="135"/>
+      <c r="D59" s="135"/>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="135"/>
+      <c r="B60" s="135"/>
+      <c r="D60" s="135"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="135"/>
+      <c r="B61" s="135"/>
+      <c r="D61" s="135"/>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="135"/>
+      <c r="B62" s="135"/>
+      <c r="D62" s="135"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="135"/>
+      <c r="B63" s="135"/>
+      <c r="D63" s="135"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="135"/>
+      <c r="B64" s="135"/>
+      <c r="D64" s="135"/>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="135"/>
+      <c r="B65" s="135"/>
+      <c r="D65" s="135"/>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="135"/>
+      <c r="B66" s="135"/>
+      <c r="D66" s="135"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="135"/>
+      <c r="B67" s="135"/>
+      <c r="D67" s="135"/>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="135"/>
+      <c r="B68" s="135"/>
+      <c r="D68" s="135"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="10" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
 </file>